--- a/tests/v1/fixtures/office6m/2026-08/bank_statements/HB_HOLD_USD_2026-07.xlsx
+++ b/tests/v1/fixtures/office6m/2026-08/bank_statements/HB_HOLD_USD_2026-07.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -476,31 +476,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FXS-20260714-HOLD</t>
+          <t>GR-2026-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fx_conversion</t>
+          <t>grant</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bought USD 1,500,000.00 / sold SGD 2,007,300.00 at 1.3382 (fund capital call 6)</t>
+          <t>GRANT GR-2026-02 Coastal Reef Restoration Society</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Harbour Bank FX desk</t>
+          <t>Coastal Reef Restoration Society</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1500000</v>
+        <v>-60000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,31 +511,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DI-DIST-B-2026-07</t>
+          <t>FXS-20260714-HOLD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>fx_conversion</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DISTRIBUTION Evergreen Income II (income)</t>
+          <t>Bought USD 1,500,000.00 / sold SGD 2,007,300.00 at 1.3382 (fund capital call 6)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bluewater Capital</t>
+          <t>Harbour Bank FX desk</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>120000</v>
+        <v>1500000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -546,12 +546,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DI-DIST-A-2026-07</t>
+          <t>DI-DIST-B-2026-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,16 +561,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DISTRIBUTION Evergreen Growth I (capital) net of withholding</t>
+          <t>DISTRIBUTION Evergreen Income II (income)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Northgate Partners</t>
+          <t>Bluewater Capital</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>262500</v>
+        <v>120000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -581,31 +581,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC-CALL-C-6</t>
+          <t>DI-DIST-A-2026-07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>capital_call</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CAPCALL Cedarpoint Ventures III No.6 ACCT 2209</t>
+          <t>DISTRIBUTION Evergreen Growth I (capital) net of withholding</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cedarpoint Ventures</t>
+          <t>Northgate Partners</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-1500000</v>
+        <v>262500</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -616,31 +616,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BF-HB-HOLD-USD-07</t>
+          <t>CC-CALL-C-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bank_fee</t>
+          <t>capital_call</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Account maintenance fee</t>
+          <t>CAPCALL Cedarpoint Ventures III No.6 ACCT 2209</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour Bank (synthetic)</t>
+          <t>Cedarpoint Ventures</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-43.24</v>
+        <v>-1500000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -651,22 +651,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IN-HB-HOLD-USD-07</t>
+          <t>BF-HB-HOLD-USD-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>bank_fee</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Credit interest</t>
+          <t>Account maintenance fee</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>36.54</v>
+        <v>-43.24</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -686,33 +686,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IN-HB-HOLD-USD-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>interest</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Credit interest</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Harbour Bank (synthetic)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>VP-QRS-0726</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>vendor_payment</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>PAY QRS-0726 Quill Research Subscriptions</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Quill Research Subscriptions</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>-4800</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -789,13 +824,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>596959.9</v>
+        <v>723709.9</v>
       </c>
       <c r="E2" t="n">
-        <v>77716.87</v>
+        <v>37716.87</v>
       </c>
       <c r="F2" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="3">
@@ -815,13 +850,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="4">
@@ -841,13 +876,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="5">
@@ -867,13 +902,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="6">
@@ -893,13 +928,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="7">
@@ -919,13 +954,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
     <row r="8">
@@ -945,13 +980,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-60000</v>
       </c>
       <c r="F8" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
     </row>
     <row r="9">
@@ -971,13 +1006,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
     </row>
     <row r="10">
@@ -997,13 +1032,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
     </row>
     <row r="11">
@@ -1023,13 +1058,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>674676.77</v>
+        <v>701426.77</v>
       </c>
       <c r="E11" t="n">
         <v>1500000</v>
       </c>
       <c r="F11" t="n">
-        <v>2174676.77</v>
+        <v>2201426.77</v>
       </c>
     </row>
     <row r="12">
@@ -1049,13 +1084,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2174676.77</v>
+        <v>2201426.77</v>
       </c>
       <c r="E12" t="n">
         <v>120000</v>
       </c>
       <c r="F12" t="n">
-        <v>2294676.77</v>
+        <v>2321426.77</v>
       </c>
     </row>
     <row r="13">
@@ -1075,13 +1110,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2294676.77</v>
+        <v>2321426.77</v>
       </c>
       <c r="E13" t="n">
         <v>262500</v>
       </c>
       <c r="F13" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
     </row>
     <row r="14">
@@ -1101,13 +1136,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
     </row>
     <row r="15">
@@ -1127,13 +1162,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
     </row>
     <row r="16">
@@ -1153,13 +1188,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2557176.77</v>
+        <v>2583926.77</v>
       </c>
       <c r="E16" t="n">
         <v>-1500000</v>
       </c>
       <c r="F16" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
     </row>
     <row r="17">
@@ -1179,13 +1214,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
     </row>
     <row r="18">
@@ -1205,13 +1240,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
     </row>
     <row r="19">
@@ -1231,13 +1266,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
     </row>
     <row r="20">
@@ -1257,13 +1292,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
     </row>
     <row r="21">
@@ -1283,13 +1318,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1057176.77</v>
+        <v>1083926.77</v>
       </c>
       <c r="E21" t="n">
         <v>-43.24</v>
       </c>
       <c r="F21" t="n">
-        <v>1057133.53</v>
+        <v>1083883.53</v>
       </c>
     </row>
     <row r="22">
@@ -1309,13 +1344,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1057133.53</v>
+        <v>1083883.53</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1057133.53</v>
+        <v>1083883.53</v>
       </c>
     </row>
     <row r="23">
@@ -1335,13 +1370,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1057133.53</v>
+        <v>1083883.53</v>
       </c>
       <c r="E23" t="n">
         <v>36.54</v>
       </c>
       <c r="F23" t="n">
-        <v>1057170.07</v>
+        <v>1083920.07</v>
       </c>
     </row>
     <row r="24">
@@ -1361,13 +1396,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1057170.07</v>
+        <v>1083920.07</v>
       </c>
       <c r="E24" t="n">
         <v>-4800</v>
       </c>
       <c r="F24" t="n">
-        <v>1052370.07</v>
+        <v>1079120.07</v>
       </c>
     </row>
   </sheetData>
